--- a/data/output/output.xlsx
+++ b/data/output/output.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NA PDF" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="eChallan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lease Deed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,546 +425,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Survey Number</t>
+          <t>Sr.no.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Land Area</t>
+          <t xml:space="preserve">Village </t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Survey No.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Order Date</t>
+          <t>Area in NA Order</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Authority Details</t>
+          <t>Dated</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Source File</t>
+          <t>NA Order No.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lease Deed Doc. No.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lease Area </t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lease Start </t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ધામણા મોટા</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>251/p2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>5,275.00 sq.mt.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ABReL SPV Limited</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>5,275.00 ચો.મી.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>16/02/2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>KALPESH RASIKBHAI UNADKAT, મામલતદાર, ધાનપુર મામલતદાર, જિ. બનાસકાંઠા</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Files/251-p2 FINAL ORDER.pdf</t>
-        </is>
-      </c>
+          <t>iORA/31/02/112/25/2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ધાનપુર મોટા</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>255</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>34,576.00 sq.mt. (out of which 16,471.00 sq.mt.)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ABReL SPV (I) Limited</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>34,576.00 sq.mt.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>08/01/2026</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>KALPESH RASIKBHAI UNADKAT, Mamlatdar, Dhana Mamlat, Dist. Gandhinagar</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Files/255 FINAL ORDER.pdf</t>
+          <t>iORA/31/02/112/9/2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>838/2025</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>16888 sq.mt.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>28/05/2025</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ધામણુ મોટા</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>16,510.00 sq.mt.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ABReL SPV (I) LIMITED</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>16,510.00 ચો.મી.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>KALPESH RASIKBHAI UNADKAT, Mamlatdar, Dhanpur, Dist. Banaskantha</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Files/256 FINAL ORDER.pdf</t>
+          <t>iORA/31/02/112/8/2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>854/2025</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>16959 sq.mt.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>28/05/2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ધાનપુર</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>16,534.00 sq.mt.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ABReL SPV (I) LIMITED</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>KALPESH RASIKBHAI UNADKAT, Mamlatdar, Dhamnanji, Dist. Banaskantha</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Files/257 FINAL ORDER.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Challan Number</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Vehicle Number</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Violation Date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Offence Description</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Payment Status</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DNR Number</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Registration Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Survey Number (New)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Village</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Land Area (SQM)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Lessor Name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Lessee Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Consideration Price</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Stamp Duty</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Registration Fee</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Source File</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>141/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>21/01/2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>251/P2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Rampura Mota</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>04047</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Rabari Harkanbhai Sonabhai</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ABReL SPV 2 Limited</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>81168</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Files/Rampura Mota S.No.- 251p2 Lease Deed No.- 141.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>838/2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+          <t>iORA/31/02/112/7/2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>837/2025</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>16792 sq.mt.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>28/05/2025</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Rampura Mota</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>16888</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Rabari Sujabhai Javanabhai</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ABReL SPV 2 Limited</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>934634.00</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40900</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10800</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Files/Rampura Mota S.No.-255 Lease Deed No.-838.pdf.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>854/2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Rampura Mota</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>16959</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rabari Mathraben Balakabhai, Rabari Rameshbhai Balakabhai, Minor Rabari Jigarbhai Balakabhai</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ABReL SPV 2 Limited</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>939116.00</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>41100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10900</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Files/Rampura Mota S.No.-256 Lease Deed No.-854.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>837/2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>28-05-2025</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Rampura Mota</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>16792</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rabari Madevabhai Manabhai</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ABReL SPV 2 Limited</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1210754.00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>52800</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>13600</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Files/Rampura Mota S.No.-257 Lease Deed No. -837.pdf.pdf</t>
         </is>
       </c>
     </row>

--- a/data/output/output.xlsx
+++ b/data/output/output.xlsx
@@ -429,13 +429,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -492,7 +492,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ધામણા મોટા</t>
+          <t>Dhanpur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5,275.00 ચો.મી.</t>
+          <t>5,275.00 sq.mt.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -515,9 +515,21 @@
           <t>iORA/31/02/112/25/2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>141/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>04047 Square Meters</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -525,7 +537,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ધાનપુર મોટા</t>
+          <t>Rampura Mota</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -535,7 +547,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34,576.00 sq.mt.</t>
+          <t>34,576.00 ચો.મી.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,17 +582,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ધામણુ મોટા</t>
+          <t>Rampura Mota</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>257</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16,510.00 ચો.મી.</t>
+          <t>16,534.00 sq.mt.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -590,17 +602,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>iORA/31/02/112/8/2026</t>
+          <t>iORA/31/02/112/7/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>854/2025</t>
+          <t>837/2025</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>16959 sq.mt.</t>
+          <t>16792 sq.mt.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -615,42 +627,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ધાનપુર</t>
+          <t>Rampura Mota</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>16,534.00 sq.mt.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>07/01/2026</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>iORA/31/02/112/7/2026</t>
-        </is>
-      </c>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>837/2025</t>
+          <t>854/2025</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16792 sq.mt.</t>
+          <t>16959 sq.mt. (4.19 Acre)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
     </row>
